--- a/artfynd/A 28716-2023 artfynd.xlsx
+++ b/artfynd/A 28716-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ39"/>
+  <dimension ref="A1:AZ55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135017526</v>
+        <v>136702664</v>
       </c>
       <c r="B2" t="n">
-        <v>92039</v>
+        <v>89470</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vallsjöberget, Ås lm</t>
+          <t>Flakaberget, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591084</v>
+        <v>591057</v>
       </c>
       <c r="R2" t="n">
-        <v>7099397</v>
+        <v>7099306</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,65 +765,65 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Julia Pettersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Julia Pettersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135017526</t>
+          <t>https://artportalen.se/Sighting/136702664</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>16891965</v>
+        <v>135017526</v>
       </c>
       <c r="B3" t="n">
-        <v>92292</v>
+        <v>92039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1506</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>3500 m Ö Granåsen, Ås lm</t>
+          <t>Vallsjöberget, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591281</v>
+        <v>591084</v>
       </c>
       <c r="R3" t="n">
-        <v>7099785</v>
+        <v>7099397</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,17 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2014-10-30</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2014-10-30</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Sveaskog naturvärdesinventering</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,65 +867,65 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16891965</t>
+          <t>https://artportalen.se/Sighting/135017526</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135017475</v>
+        <v>136702647</v>
       </c>
       <c r="B4" t="n">
-        <v>92006</v>
+        <v>92538</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vallsjöberget, Ås lm</t>
+          <t>Flakaberget, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>591268</v>
+        <v>591183</v>
       </c>
       <c r="R4" t="n">
-        <v>7099457</v>
+        <v>7099542</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -954,12 +949,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,65 +969,65 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Julia Pettersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Julia Pettersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135017475</t>
+          <t>https://artportalen.se/Sighting/136702647</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>16891479</v>
+        <v>136702648</v>
       </c>
       <c r="B5" t="n">
-        <v>79327</v>
+        <v>92538</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>3500 m OSO Granåsen, Ås lm</t>
+          <t>Flakaberget, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591268</v>
+        <v>591180</v>
       </c>
       <c r="R5" t="n">
-        <v>7099396</v>
+        <v>7099538</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1056,17 +1051,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2014-10-30</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2014-10-30</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Sveaskog naturvärdesinventering</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1081,65 +1071,65 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Julia Pettersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Julia Pettersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16891479</t>
+          <t>https://artportalen.se/Sighting/136702648</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>16891490</v>
+        <v>136702629</v>
       </c>
       <c r="B6" t="n">
-        <v>79327</v>
+        <v>83341</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>3400 m Ö Granåsen, Ås lm</t>
+          <t>Flakaberget, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>591211</v>
+        <v>591035</v>
       </c>
       <c r="R6" t="n">
-        <v>7099657</v>
+        <v>7099358</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1163,17 +1153,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2014-10-30</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2014-10-30</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Sveaskog naturvärdesinventering</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1188,65 +1173,65 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Julia Pettersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Julia Pettersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16891490</t>
+          <t>https://artportalen.se/Sighting/136702629</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135017553</v>
+        <v>136702662</v>
       </c>
       <c r="B7" t="n">
-        <v>79438</v>
+        <v>83341</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vallsjöberget, Ås lm</t>
+          <t>Flakaberget, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>591108</v>
+        <v>591149</v>
       </c>
       <c r="R7" t="n">
-        <v>7099339</v>
+        <v>7099646</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1270,12 +1255,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1290,65 +1275,65 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Julia Pettersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Julia Pettersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135017553</t>
+          <t>https://artportalen.se/Sighting/136702662</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135017554</v>
+        <v>136702663</v>
       </c>
       <c r="B8" t="n">
-        <v>79438</v>
+        <v>83341</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Vallsjöberget, Ås lm</t>
+          <t>Flakaberget, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>591092</v>
+        <v>591063</v>
       </c>
       <c r="R8" t="n">
-        <v>7099380</v>
+        <v>7099386</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1372,12 +1357,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1392,27 +1377,27 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Julia Pettersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Julia Pettersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135017554</t>
+          <t>https://artportalen.se/Sighting/136702663</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135017555</v>
+        <v>16891965</v>
       </c>
       <c r="B9" t="n">
-        <v>79438</v>
+        <v>92292</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1420,37 +1405,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1506</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Vallsjöberget, Ås lm</t>
+          <t>3500 m Ö Granåsen, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>591077</v>
+        <v>591281</v>
       </c>
       <c r="R9" t="n">
-        <v>7099412</v>
+        <v>7099785</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1474,12 +1459,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2014-10-30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2014-10-30</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Sveaskog naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1494,65 +1484,65 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135017555</t>
+          <t>https://artportalen.se/Sighting/16891965</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135017556</v>
+        <v>136702641</v>
       </c>
       <c r="B10" t="n">
-        <v>79438</v>
+        <v>80590</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Vallsjöberget, Ås lm</t>
+          <t>Flakaberget, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>591081</v>
+        <v>591072</v>
       </c>
       <c r="R10" t="n">
-        <v>7099420</v>
+        <v>7099413</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1576,12 +1566,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1596,49 +1586,49 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Julia Pettersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Julia Pettersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135017556</t>
+          <t>https://artportalen.se/Sighting/136702641</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135017557</v>
+        <v>135017475</v>
       </c>
       <c r="B11" t="n">
-        <v>79438</v>
+        <v>92006</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1648,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>591105</v>
+        <v>591268</v>
       </c>
       <c r="R11" t="n">
-        <v>7099439</v>
+        <v>7099457</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1709,54 +1699,54 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135017557</t>
+          <t>https://artportalen.se/Sighting/135017475</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135017558</v>
+        <v>136702632</v>
       </c>
       <c r="B12" t="n">
-        <v>79438</v>
+        <v>92069</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vallsjöberget, Ås lm</t>
+          <t>Flakaberget, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>591121</v>
+        <v>591161</v>
       </c>
       <c r="R12" t="n">
-        <v>7099515</v>
+        <v>7099516</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1780,12 +1770,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1800,27 +1790,27 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Julia Pettersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Julia Pettersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135017558</t>
+          <t>https://artportalen.se/Sighting/136702632</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135017559</v>
+        <v>16891479</v>
       </c>
       <c r="B13" t="n">
-        <v>79438</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1848,17 +1838,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vallsjöberget, Ås lm</t>
+          <t>3500 m OSO Granåsen, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>591127</v>
+        <v>591268</v>
       </c>
       <c r="R13" t="n">
-        <v>7099530</v>
+        <v>7099396</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1882,12 +1872,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2014-10-30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2014-10-30</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Sveaskog naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1902,27 +1897,27 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135017559</t>
+          <t>https://artportalen.se/Sighting/16891479</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135017560</v>
+        <v>16891490</v>
       </c>
       <c r="B14" t="n">
-        <v>79438</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1950,17 +1945,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Vallsjöberget, Ås lm</t>
+          <t>3400 m Ö Granåsen, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>591148</v>
+        <v>591211</v>
       </c>
       <c r="R14" t="n">
-        <v>7099535</v>
+        <v>7099657</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1984,12 +1979,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2014-10-30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2014-10-30</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Sveaskog naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2004,24 +2004,24 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135017560</t>
+          <t>https://artportalen.se/Sighting/16891490</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135017561</v>
+        <v>135017553</v>
       </c>
       <c r="B15" t="n">
         <v>79438</v>
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>591163</v>
+        <v>591108</v>
       </c>
       <c r="R15" t="n">
-        <v>7099540</v>
+        <v>7099339</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2117,13 +2117,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135017561</t>
+          <t>https://artportalen.se/Sighting/135017553</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135017562</v>
+        <v>135017554</v>
       </c>
       <c r="B16" t="n">
         <v>79438</v>
@@ -2158,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>591175</v>
+        <v>591092</v>
       </c>
       <c r="R16" t="n">
-        <v>7099551</v>
+        <v>7099380</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2219,13 +2219,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135017562</t>
+          <t>https://artportalen.se/Sighting/135017554</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135017563</v>
+        <v>135017555</v>
       </c>
       <c r="B17" t="n">
         <v>79438</v>
@@ -2260,10 +2260,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>591220</v>
+        <v>591077</v>
       </c>
       <c r="R17" t="n">
-        <v>7099516</v>
+        <v>7099412</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2321,13 +2321,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135017563</t>
+          <t>https://artportalen.se/Sighting/135017555</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135017564</v>
+        <v>135017556</v>
       </c>
       <c r="B18" t="n">
         <v>79438</v>
@@ -2362,10 +2362,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>591255</v>
+        <v>591081</v>
       </c>
       <c r="R18" t="n">
-        <v>7099476</v>
+        <v>7099420</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2423,13 +2423,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135017564</t>
+          <t>https://artportalen.se/Sighting/135017556</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135017565</v>
+        <v>135017557</v>
       </c>
       <c r="B19" t="n">
         <v>79438</v>
@@ -2464,10 +2464,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>591314</v>
+        <v>591105</v>
       </c>
       <c r="R19" t="n">
-        <v>7099415</v>
+        <v>7099439</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2502,11 +2502,6 @@
           <t>2026-07-08</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2530,54 +2525,54 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135017565</t>
+          <t>https://artportalen.se/Sighting/135017557</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>16891921</v>
+        <v>135017558</v>
       </c>
       <c r="B20" t="n">
-        <v>80432</v>
+        <v>79438</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>3400 m Ö Granåsen, Ås lm</t>
+          <t>Vallsjöberget, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>591217</v>
+        <v>591121</v>
       </c>
       <c r="R20" t="n">
-        <v>7099674</v>
+        <v>7099515</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2601,17 +2596,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2014-10-30</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2014-10-30</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Sveaskog naturvärdesinventering</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2626,49 +2616,49 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16891921</t>
+          <t>https://artportalen.se/Sighting/135017558</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135017514</v>
+        <v>135017559</v>
       </c>
       <c r="B21" t="n">
-        <v>80553</v>
+        <v>79438</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2678,10 +2668,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>591173</v>
+        <v>591127</v>
       </c>
       <c r="R21" t="n">
-        <v>7099532</v>
+        <v>7099530</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2739,54 +2729,54 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135017514</t>
+          <t>https://artportalen.se/Sighting/135017559</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>136487005</v>
+        <v>135017560</v>
       </c>
       <c r="B22" t="n">
-        <v>80589</v>
+        <v>79438</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Flakaberget, Ås lm</t>
+          <t>Vallsjöberget, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>590966</v>
+        <v>591148</v>
       </c>
       <c r="R22" t="n">
-        <v>7099401</v>
+        <v>7099535</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2810,12 +2800,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2830,65 +2820,65 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136487005</t>
+          <t>https://artportalen.se/Sighting/135017560</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>16892197</v>
+        <v>135017561</v>
       </c>
       <c r="B23" t="n">
-        <v>80461</v>
+        <v>79438</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>3400 m Ö Granåsen, Ås lm</t>
+          <t>Vallsjöberget, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>591217</v>
+        <v>591163</v>
       </c>
       <c r="R23" t="n">
-        <v>7099675</v>
+        <v>7099540</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2912,17 +2902,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2014-10-30</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2014-10-30</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Sveaskog naturvärdesinventering</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2937,49 +2922,49 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16892197</t>
+          <t>https://artportalen.se/Sighting/135017561</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135017501</v>
+        <v>135017562</v>
       </c>
       <c r="B24" t="n">
-        <v>80558</v>
+        <v>79438</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2989,10 +2974,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>591153</v>
+        <v>591175</v>
       </c>
       <c r="R24" t="n">
-        <v>7099534</v>
+        <v>7099551</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3050,33 +3035,33 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135017501</t>
+          <t>https://artportalen.se/Sighting/135017562</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>16891272</v>
+        <v>135017563</v>
       </c>
       <c r="B25" t="n">
-        <v>80467</v>
+        <v>79438</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3087,17 +3072,17 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>3400 m Ö Granåsen, Ås lm</t>
+          <t>Vallsjöberget, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>591162</v>
+        <v>591220</v>
       </c>
       <c r="R25" t="n">
-        <v>7099535</v>
+        <v>7099516</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3121,17 +3106,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2014-10-30</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2014-10-30</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Sveaskog naturvärdesinventering</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3146,49 +3126,49 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16891272</t>
+          <t>https://artportalen.se/Sighting/135017563</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135017566</v>
+        <v>135017564</v>
       </c>
       <c r="B26" t="n">
-        <v>99186</v>
+        <v>79438</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3198,10 +3178,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>591274</v>
+        <v>591255</v>
       </c>
       <c r="R26" t="n">
-        <v>7099457</v>
+        <v>7099476</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3242,7 +3222,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3260,38 +3239,38 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135017566</t>
+          <t>https://artportalen.se/Sighting/135017564</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135017569</v>
+        <v>135017565</v>
       </c>
       <c r="B27" t="n">
-        <v>99186</v>
+        <v>79438</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3301,10 +3280,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>591148</v>
+        <v>591314</v>
       </c>
       <c r="R27" t="n">
-        <v>7099523</v>
+        <v>7099415</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3339,6 +3318,11 @@
           <t>2026-07-08</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3362,54 +3346,54 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135017569</t>
+          <t>https://artportalen.se/Sighting/135017565</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135017570</v>
+        <v>136702660</v>
       </c>
       <c r="B28" t="n">
-        <v>99186</v>
+        <v>79474</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Vallsjöberget, Ås lm</t>
+          <t>Flakaberget, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>591178</v>
+        <v>591160</v>
       </c>
       <c r="R28" t="n">
-        <v>7099537</v>
+        <v>7099588</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3433,12 +3417,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3453,65 +3437,65 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Julia Pettersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Julia Pettersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135017570</t>
+          <t>https://artportalen.se/Sighting/136702660</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135017572</v>
+        <v>136702661</v>
       </c>
       <c r="B29" t="n">
-        <v>98290</v>
+        <v>79474</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219815</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ekbräken</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Gymnocarpium dryopteris</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Newman</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Vallsjöberget, Ås lm</t>
+          <t>Flakaberget, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>591268</v>
+        <v>591043</v>
       </c>
       <c r="R29" t="n">
-        <v>7099456</v>
+        <v>7099363</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3535,12 +3519,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3555,65 +3539,65 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Julia Pettersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Julia Pettersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135017572</t>
+          <t>https://artportalen.se/Sighting/136702661</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135017518</v>
+        <v>136702630</v>
       </c>
       <c r="B30" t="n">
-        <v>111237</v>
+        <v>83461</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220240</v>
+        <v>6440</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Vallsjöberget, Ås lm</t>
+          <t>Flakaberget, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>591204</v>
+        <v>591035</v>
       </c>
       <c r="R30" t="n">
-        <v>7099540</v>
+        <v>7099358</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3637,12 +3621,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3657,27 +3641,27 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Julia Pettersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Julia Pettersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135017518</t>
+          <t>https://artportalen.se/Sighting/136702630</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135017498</v>
+        <v>136702644</v>
       </c>
       <c r="B31" t="n">
-        <v>110007</v>
+        <v>80483</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3685,37 +3669,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221184</v>
+        <v>6456</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Torta</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lactuca alpina</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Vallsjöberget, Ås lm</t>
+          <t>Flakaberget, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>591238</v>
+        <v>591111</v>
       </c>
       <c r="R31" t="n">
-        <v>7099483</v>
+        <v>7099668</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3739,12 +3723,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3759,27 +3743,27 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Julia Pettersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Julia Pettersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135017498</t>
+          <t>https://artportalen.se/Sighting/136702644</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135017499</v>
+        <v>136702645</v>
       </c>
       <c r="B32" t="n">
-        <v>110007</v>
+        <v>80483</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3787,37 +3771,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221184</v>
+        <v>6456</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Torta</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lactuca alpina</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Vallsjöberget, Ås lm</t>
+          <t>Flakaberget, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>591279</v>
+        <v>591129</v>
       </c>
       <c r="R32" t="n">
-        <v>7099455</v>
+        <v>7099645</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3841,12 +3825,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3861,65 +3845,65 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Julia Pettersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Julia Pettersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135017499</t>
+          <t>https://artportalen.se/Sighting/136702645</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135017511</v>
+        <v>16891921</v>
       </c>
       <c r="B33" t="n">
-        <v>98131</v>
+        <v>80432</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Vallsjöberget, Ås lm</t>
+          <t>3400 m Ö Granåsen, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>591204</v>
+        <v>591217</v>
       </c>
       <c r="R33" t="n">
-        <v>7099540</v>
+        <v>7099674</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3943,12 +3927,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2014-10-30</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2014-10-30</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Sveaskog naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3963,49 +3952,49 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135017511</t>
+          <t>https://artportalen.se/Sighting/16891921</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135017508</v>
+        <v>135017514</v>
       </c>
       <c r="B34" t="n">
-        <v>99291</v>
+        <v>80553</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4015,10 +4004,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>591115</v>
+        <v>591173</v>
       </c>
       <c r="R34" t="n">
-        <v>7099452</v>
+        <v>7099532</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4076,54 +4065,54 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135017508</t>
+          <t>https://artportalen.se/Sighting/135017514</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135017509</v>
+        <v>136487005</v>
       </c>
       <c r="B35" t="n">
-        <v>99291</v>
+        <v>80589</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Vallsjöberget, Ås lm</t>
+          <t>Flakaberget, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>591110</v>
+        <v>590966</v>
       </c>
       <c r="R35" t="n">
-        <v>7099504</v>
+        <v>7099401</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4147,12 +4136,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4167,65 +4156,65 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135017509</t>
+          <t>https://artportalen.se/Sighting/136487005</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135017510</v>
+        <v>136702650</v>
       </c>
       <c r="B36" t="n">
-        <v>99291</v>
+        <v>80589</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Vallsjöberget, Ås lm</t>
+          <t>Flakaberget, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>591144</v>
+        <v>591175</v>
       </c>
       <c r="R36" t="n">
-        <v>7099533</v>
+        <v>7099531</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4249,12 +4238,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4269,27 +4258,27 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Julia Pettersson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Julia Pettersson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135017510</t>
+          <t>https://artportalen.se/Sighting/136702650</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135017512</v>
+        <v>16892197</v>
       </c>
       <c r="B37" t="n">
-        <v>98348</v>
+        <v>80461</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4297,37 +4286,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222736</v>
+        <v>6462</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Majbräken</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Athyrium filix-femina</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Vallsjöberget, Ås lm</t>
+          <t>3400 m Ö Granåsen, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>591190</v>
+        <v>591217</v>
       </c>
       <c r="R37" t="n">
-        <v>7099540</v>
+        <v>7099675</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4351,12 +4340,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2014-10-30</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2014-10-30</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Sveaskog naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4371,27 +4365,27 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135017512</t>
+          <t>https://artportalen.se/Sighting/16892197</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135017522</v>
+        <v>135017501</v>
       </c>
       <c r="B38" t="n">
-        <v>98320</v>
+        <v>80558</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4399,21 +4393,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>223358</v>
+        <v>6462</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4423,10 +4417,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>591239</v>
+        <v>591153</v>
       </c>
       <c r="R38" t="n">
-        <v>7099484</v>
+        <v>7099534</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4484,16 +4478,16 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135017522</t>
+          <t>https://artportalen.se/Sighting/135017501</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135017523</v>
+        <v>16891272</v>
       </c>
       <c r="B39" t="n">
-        <v>98320</v>
+        <v>80467</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4501,37 +4495,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>223358</v>
+        <v>6463</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Vallsjöberget, Ås lm</t>
+          <t>3400 m Ö Granåsen, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>591280</v>
+        <v>591162</v>
       </c>
       <c r="R39" t="n">
-        <v>7099457</v>
+        <v>7099535</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4555,12 +4549,17 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2014-10-30</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2014-10-30</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Sveaskog naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4575,16 +4574,1649 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16891272</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>136702636</v>
+      </c>
+      <c r="B40" t="n">
+        <v>58003</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Flakaberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>591045</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7099363</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Julia Pettersson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Julia Pettersson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136702636</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>135017566</v>
+      </c>
+      <c r="B41" t="n">
+        <v>99186</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Vallsjöberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>591274</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7099457</v>
+      </c>
+      <c r="S41" t="n">
+        <v>25</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135017566</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>135017569</v>
+      </c>
+      <c r="B42" t="n">
+        <v>99186</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Vallsjöberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>591148</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7099523</v>
+      </c>
+      <c r="S42" t="n">
+        <v>25</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135017569</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>135017570</v>
+      </c>
+      <c r="B43" t="n">
+        <v>99186</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Vallsjöberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>591178</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7099537</v>
+      </c>
+      <c r="S43" t="n">
+        <v>25</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135017570</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>135017572</v>
+      </c>
+      <c r="B44" t="n">
+        <v>98290</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>219815</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Ekbräken</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Gymnocarpium dryopteris</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) Newman</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Vallsjöberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>591268</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7099456</v>
+      </c>
+      <c r="S44" t="n">
+        <v>25</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135017572</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>135017518</v>
+      </c>
+      <c r="B45" t="n">
+        <v>111237</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Vallsjöberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>591204</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7099540</v>
+      </c>
+      <c r="S45" t="n">
+        <v>25</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135017518</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>135017498</v>
+      </c>
+      <c r="B46" t="n">
+        <v>110007</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>221184</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Torta</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Lactuca alpina</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Vallsjöberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>591238</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7099483</v>
+      </c>
+      <c r="S46" t="n">
+        <v>25</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135017498</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>135017499</v>
+      </c>
+      <c r="B47" t="n">
+        <v>110007</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>221184</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Torta</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Lactuca alpina</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Vallsjöberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>591279</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7099455</v>
+      </c>
+      <c r="S47" t="n">
+        <v>25</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135017499</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>136702634</v>
+      </c>
+      <c r="B48" t="n">
+        <v>110091</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>221184</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Torta</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Lactuca alpina</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Flakaberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>591107</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7099516</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Julia Pettersson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Julia Pettersson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136702634</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>135017511</v>
+      </c>
+      <c r="B49" t="n">
+        <v>98131</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Vallsjöberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>591204</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7099540</v>
+      </c>
+      <c r="S49" t="n">
+        <v>25</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135017511</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>135017508</v>
+      </c>
+      <c r="B50" t="n">
+        <v>99291</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Vallsjöberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>591115</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7099452</v>
+      </c>
+      <c r="S50" t="n">
+        <v>25</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135017508</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>135017509</v>
+      </c>
+      <c r="B51" t="n">
+        <v>99291</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Vallsjöberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>591110</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7099504</v>
+      </c>
+      <c r="S51" t="n">
+        <v>25</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135017509</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>135017510</v>
+      </c>
+      <c r="B52" t="n">
+        <v>99291</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Vallsjöberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>591144</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7099533</v>
+      </c>
+      <c r="S52" t="n">
+        <v>25</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135017510</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>135017512</v>
+      </c>
+      <c r="B53" t="n">
+        <v>98348</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>222736</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Majbräken</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Athyrium filix-femina</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Vallsjöberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>591190</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7099540</v>
+      </c>
+      <c r="S53" t="n">
+        <v>25</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135017512</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>135017522</v>
+      </c>
+      <c r="B54" t="n">
+        <v>98320</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Vallsjöberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>591239</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7099484</v>
+      </c>
+      <c r="S54" t="n">
+        <v>25</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135017522</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>135017523</v>
+      </c>
+      <c r="B55" t="n">
+        <v>98320</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Vallsjöberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>591280</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7099457</v>
+      </c>
+      <c r="S55" t="n">
+        <v>25</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135017523</t>
         </is>
@@ -4630,6 +6262,22 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28716-2023 artfynd.xlsx
+++ b/artfynd/A 28716-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136702664</v>
       </c>
       <c r="B2" t="n">
-        <v>89470</v>
+        <v>89472</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136702647</v>
       </c>
       <c r="B4" t="n">
-        <v>92538</v>
+        <v>92543</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136702648</v>
       </c>
       <c r="B5" t="n">
-        <v>92538</v>
+        <v>92543</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136702629</v>
       </c>
       <c r="B6" t="n">
-        <v>83341</v>
+        <v>83343</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136702662</v>
       </c>
       <c r="B7" t="n">
-        <v>83341</v>
+        <v>83343</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136702663</v>
       </c>
       <c r="B8" t="n">
-        <v>83341</v>
+        <v>83343</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>136702641</v>
       </c>
       <c r="B10" t="n">
-        <v>80590</v>
+        <v>80592</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>136702632</v>
       </c>
       <c r="B12" t="n">
-        <v>92069</v>
+        <v>92074</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3355,7 +3355,7 @@
         <v>136702660</v>
       </c>
       <c r="B28" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         <v>136702661</v>
       </c>
       <c r="B29" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         <v>136702630</v>
       </c>
       <c r="B30" t="n">
-        <v>83461</v>
+        <v>83463</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>136702644</v>
       </c>
       <c r="B31" t="n">
-        <v>80483</v>
+        <v>80485</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         <v>136702645</v>
       </c>
       <c r="B32" t="n">
-        <v>80483</v>
+        <v>80485</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>136487005</v>
       </c>
       <c r="B35" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>136702650</v>
       </c>
       <c r="B36" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         <v>136702636</v>
       </c>
       <c r="B40" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         <v>136702634</v>
       </c>
       <c r="B48" t="n">
-        <v>110091</v>
+        <v>110096</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 28716-2023 artfynd.xlsx
+++ b/artfynd/A 28716-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136702664</v>
       </c>
       <c r="B2" t="n">
-        <v>89472</v>
+        <v>89474</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136702647</v>
       </c>
       <c r="B4" t="n">
-        <v>92543</v>
+        <v>92545</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136702648</v>
       </c>
       <c r="B5" t="n">
-        <v>92543</v>
+        <v>92545</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>136702632</v>
       </c>
       <c r="B12" t="n">
-        <v>92074</v>
+        <v>92076</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         <v>136702634</v>
       </c>
       <c r="B48" t="n">
-        <v>110096</v>
+        <v>110098</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 28716-2023 artfynd.xlsx
+++ b/artfynd/A 28716-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136702664</v>
       </c>
       <c r="B2" t="n">
-        <v>89474</v>
+        <v>89476</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136702647</v>
       </c>
       <c r="B4" t="n">
-        <v>92545</v>
+        <v>92547</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136702648</v>
       </c>
       <c r="B5" t="n">
-        <v>92545</v>
+        <v>92547</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136702629</v>
       </c>
       <c r="B6" t="n">
-        <v>83343</v>
+        <v>83347</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136702662</v>
       </c>
       <c r="B7" t="n">
-        <v>83343</v>
+        <v>83347</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136702663</v>
       </c>
       <c r="B8" t="n">
-        <v>83343</v>
+        <v>83347</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>136702641</v>
       </c>
       <c r="B10" t="n">
-        <v>80592</v>
+        <v>80596</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>136702632</v>
       </c>
       <c r="B12" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3355,7 +3355,7 @@
         <v>136702660</v>
       </c>
       <c r="B28" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         <v>136702661</v>
       </c>
       <c r="B29" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         <v>136702630</v>
       </c>
       <c r="B30" t="n">
-        <v>83463</v>
+        <v>83467</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>136702644</v>
       </c>
       <c r="B31" t="n">
-        <v>80485</v>
+        <v>80489</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         <v>136702645</v>
       </c>
       <c r="B32" t="n">
-        <v>80485</v>
+        <v>80489</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>136487005</v>
       </c>
       <c r="B35" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>136702650</v>
       </c>
       <c r="B36" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         <v>136702634</v>
       </c>
       <c r="B48" t="n">
-        <v>110098</v>
+        <v>110104</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 28716-2023 artfynd.xlsx
+++ b/artfynd/A 28716-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136702664</v>
       </c>
       <c r="B2" t="n">
-        <v>89476</v>
+        <v>89478</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136702647</v>
       </c>
       <c r="B4" t="n">
-        <v>92547</v>
+        <v>92549</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136702648</v>
       </c>
       <c r="B5" t="n">
-        <v>92547</v>
+        <v>92549</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136702629</v>
       </c>
       <c r="B6" t="n">
-        <v>83347</v>
+        <v>83349</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136702662</v>
       </c>
       <c r="B7" t="n">
-        <v>83347</v>
+        <v>83349</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136702663</v>
       </c>
       <c r="B8" t="n">
-        <v>83347</v>
+        <v>83349</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>136702641</v>
       </c>
       <c r="B10" t="n">
-        <v>80596</v>
+        <v>80598</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>136702632</v>
       </c>
       <c r="B12" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3355,7 +3355,7 @@
         <v>136702660</v>
       </c>
       <c r="B28" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         <v>136702661</v>
       </c>
       <c r="B29" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         <v>136702630</v>
       </c>
       <c r="B30" t="n">
-        <v>83467</v>
+        <v>83469</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>136702644</v>
       </c>
       <c r="B31" t="n">
-        <v>80489</v>
+        <v>80491</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         <v>136702645</v>
       </c>
       <c r="B32" t="n">
-        <v>80489</v>
+        <v>80491</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>136487005</v>
       </c>
       <c r="B35" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>136702650</v>
       </c>
       <c r="B36" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         <v>136702634</v>
       </c>
       <c r="B48" t="n">
-        <v>110104</v>
+        <v>110106</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 28716-2023 artfynd.xlsx
+++ b/artfynd/A 28716-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136702664</v>
       </c>
       <c r="B2" t="n">
-        <v>89478</v>
+        <v>89479</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136702647</v>
       </c>
       <c r="B4" t="n">
-        <v>92549</v>
+        <v>92550</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136702648</v>
       </c>
       <c r="B5" t="n">
-        <v>92549</v>
+        <v>92550</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136702629</v>
       </c>
       <c r="B6" t="n">
-        <v>83349</v>
+        <v>83350</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136702662</v>
       </c>
       <c r="B7" t="n">
-        <v>83349</v>
+        <v>83350</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136702663</v>
       </c>
       <c r="B8" t="n">
-        <v>83349</v>
+        <v>83350</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>136702641</v>
       </c>
       <c r="B10" t="n">
-        <v>80598</v>
+        <v>80599</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>136702632</v>
       </c>
       <c r="B12" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3355,7 +3355,7 @@
         <v>136702660</v>
       </c>
       <c r="B28" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         <v>136702661</v>
       </c>
       <c r="B29" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         <v>136702630</v>
       </c>
       <c r="B30" t="n">
-        <v>83469</v>
+        <v>83470</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>136702644</v>
       </c>
       <c r="B31" t="n">
-        <v>80491</v>
+        <v>80492</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         <v>136702645</v>
       </c>
       <c r="B32" t="n">
-        <v>80491</v>
+        <v>80492</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>136487005</v>
       </c>
       <c r="B35" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>136702650</v>
       </c>
       <c r="B36" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         <v>136702634</v>
       </c>
       <c r="B48" t="n">
-        <v>110106</v>
+        <v>110107</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 28716-2023 artfynd.xlsx
+++ b/artfynd/A 28716-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136702664</v>
       </c>
       <c r="B2" t="n">
-        <v>89479</v>
+        <v>89485</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136702647</v>
       </c>
       <c r="B4" t="n">
-        <v>92550</v>
+        <v>92556</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136702648</v>
       </c>
       <c r="B5" t="n">
-        <v>92550</v>
+        <v>92556</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>136702632</v>
       </c>
       <c r="B12" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         <v>136702634</v>
       </c>
       <c r="B48" t="n">
-        <v>110107</v>
+        <v>110113</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 28716-2023 artfynd.xlsx
+++ b/artfynd/A 28716-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136702664</v>
       </c>
       <c r="B2" t="n">
-        <v>89485</v>
+        <v>89489</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136702647</v>
       </c>
       <c r="B4" t="n">
-        <v>92556</v>
+        <v>92560</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136702648</v>
       </c>
       <c r="B5" t="n">
-        <v>92556</v>
+        <v>92560</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136702629</v>
       </c>
       <c r="B6" t="n">
-        <v>83350</v>
+        <v>83354</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136702662</v>
       </c>
       <c r="B7" t="n">
-        <v>83350</v>
+        <v>83354</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136702663</v>
       </c>
       <c r="B8" t="n">
-        <v>83350</v>
+        <v>83354</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>136702641</v>
       </c>
       <c r="B10" t="n">
-        <v>80599</v>
+        <v>80601</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>136702632</v>
       </c>
       <c r="B12" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3355,7 +3355,7 @@
         <v>136702660</v>
       </c>
       <c r="B28" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         <v>136702661</v>
       </c>
       <c r="B29" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         <v>136702630</v>
       </c>
       <c r="B30" t="n">
-        <v>83470</v>
+        <v>83474</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>136702644</v>
       </c>
       <c r="B31" t="n">
-        <v>80492</v>
+        <v>80494</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         <v>136702645</v>
       </c>
       <c r="B32" t="n">
-        <v>80492</v>
+        <v>80494</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>136487005</v>
       </c>
       <c r="B35" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>136702650</v>
       </c>
       <c r="B36" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         <v>136702634</v>
       </c>
       <c r="B48" t="n">
-        <v>110113</v>
+        <v>110117</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 28716-2023 artfynd.xlsx
+++ b/artfynd/A 28716-2023 artfynd.xlsx
@@ -5411,7 +5411,7 @@
         <v>136702634</v>
       </c>
       <c r="B48" t="n">
-        <v>110117</v>
+        <v>110119</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 28716-2023 artfynd.xlsx
+++ b/artfynd/A 28716-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136702664</v>
       </c>
       <c r="B2" t="n">
-        <v>89489</v>
+        <v>89491</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136702647</v>
       </c>
       <c r="B4" t="n">
-        <v>92560</v>
+        <v>92562</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136702648</v>
       </c>
       <c r="B5" t="n">
-        <v>92560</v>
+        <v>92562</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136702629</v>
       </c>
       <c r="B6" t="n">
-        <v>83354</v>
+        <v>83356</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136702662</v>
       </c>
       <c r="B7" t="n">
-        <v>83354</v>
+        <v>83356</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136702663</v>
       </c>
       <c r="B8" t="n">
-        <v>83354</v>
+        <v>83356</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>136702641</v>
       </c>
       <c r="B10" t="n">
-        <v>80601</v>
+        <v>80604</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>136702632</v>
       </c>
       <c r="B12" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3355,7 +3355,7 @@
         <v>136702660</v>
       </c>
       <c r="B28" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         <v>136702661</v>
       </c>
       <c r="B29" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         <v>136702630</v>
       </c>
       <c r="B30" t="n">
-        <v>83474</v>
+        <v>83476</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>136702644</v>
       </c>
       <c r="B31" t="n">
-        <v>80494</v>
+        <v>80497</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         <v>136702645</v>
       </c>
       <c r="B32" t="n">
-        <v>80494</v>
+        <v>80497</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>136702650</v>
       </c>
       <c r="B36" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         <v>136702634</v>
       </c>
       <c r="B48" t="n">
-        <v>110119</v>
+        <v>110121</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 28716-2023 artfynd.xlsx
+++ b/artfynd/A 28716-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136702664</v>
       </c>
       <c r="B2" t="n">
-        <v>89491</v>
+        <v>89504</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136702647</v>
       </c>
       <c r="B4" t="n">
-        <v>92562</v>
+        <v>92575</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136702648</v>
       </c>
       <c r="B5" t="n">
-        <v>92562</v>
+        <v>92575</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136702629</v>
       </c>
       <c r="B6" t="n">
-        <v>83356</v>
+        <v>83369</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136702662</v>
       </c>
       <c r="B7" t="n">
-        <v>83356</v>
+        <v>83369</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136702663</v>
       </c>
       <c r="B8" t="n">
-        <v>83356</v>
+        <v>83369</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>136702641</v>
       </c>
       <c r="B10" t="n">
-        <v>80604</v>
+        <v>80617</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>136702632</v>
       </c>
       <c r="B12" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3355,7 +3355,7 @@
         <v>136702660</v>
       </c>
       <c r="B28" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         <v>136702661</v>
       </c>
       <c r="B29" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         <v>136702630</v>
       </c>
       <c r="B30" t="n">
-        <v>83476</v>
+        <v>83489</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>136702644</v>
       </c>
       <c r="B31" t="n">
-        <v>80497</v>
+        <v>80510</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         <v>136702645</v>
       </c>
       <c r="B32" t="n">
-        <v>80497</v>
+        <v>80510</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>136702650</v>
       </c>
       <c r="B36" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         <v>136702636</v>
       </c>
       <c r="B40" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         <v>136702634</v>
       </c>
       <c r="B48" t="n">
-        <v>110121</v>
+        <v>110134</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 28716-2023 artfynd.xlsx
+++ b/artfynd/A 28716-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136702664</v>
       </c>
       <c r="B2" t="n">
-        <v>89504</v>
+        <v>89506</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136702647</v>
       </c>
       <c r="B4" t="n">
-        <v>92575</v>
+        <v>92577</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136702648</v>
       </c>
       <c r="B5" t="n">
-        <v>92575</v>
+        <v>92577</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136702629</v>
       </c>
       <c r="B6" t="n">
-        <v>83369</v>
+        <v>83371</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136702662</v>
       </c>
       <c r="B7" t="n">
-        <v>83369</v>
+        <v>83371</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136702663</v>
       </c>
       <c r="B8" t="n">
-        <v>83369</v>
+        <v>83371</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>136702641</v>
       </c>
       <c r="B10" t="n">
-        <v>80617</v>
+        <v>80619</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>136702632</v>
       </c>
       <c r="B12" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3355,7 +3355,7 @@
         <v>136702660</v>
       </c>
       <c r="B28" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         <v>136702661</v>
       </c>
       <c r="B29" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         <v>136702630</v>
       </c>
       <c r="B30" t="n">
-        <v>83489</v>
+        <v>83491</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>136702644</v>
       </c>
       <c r="B31" t="n">
-        <v>80510</v>
+        <v>80512</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         <v>136702645</v>
       </c>
       <c r="B32" t="n">
-        <v>80510</v>
+        <v>80512</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>136702650</v>
       </c>
       <c r="B36" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         <v>136702636</v>
       </c>
       <c r="B40" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         <v>136702634</v>
       </c>
       <c r="B48" t="n">
-        <v>110134</v>
+        <v>110136</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 28716-2023 artfynd.xlsx
+++ b/artfynd/A 28716-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136702664</v>
       </c>
       <c r="B2" t="n">
-        <v>89506</v>
+        <v>89509</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136702647</v>
       </c>
       <c r="B4" t="n">
-        <v>92577</v>
+        <v>92580</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136702648</v>
       </c>
       <c r="B5" t="n">
-        <v>92577</v>
+        <v>92580</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>136702632</v>
       </c>
       <c r="B12" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         <v>136702630</v>
       </c>
       <c r="B30" t="n">
-        <v>83491</v>
+        <v>83494</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         <v>136702634</v>
       </c>
       <c r="B48" t="n">
-        <v>110136</v>
+        <v>110141</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 28716-2023 artfynd.xlsx
+++ b/artfynd/A 28716-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136702664</v>
       </c>
       <c r="B2" t="n">
-        <v>89509</v>
+        <v>89519</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136702647</v>
       </c>
       <c r="B4" t="n">
-        <v>92580</v>
+        <v>92590</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136702648</v>
       </c>
       <c r="B5" t="n">
-        <v>92580</v>
+        <v>92590</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136702629</v>
       </c>
       <c r="B6" t="n">
-        <v>83371</v>
+        <v>83381</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136702662</v>
       </c>
       <c r="B7" t="n">
-        <v>83371</v>
+        <v>83381</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136702663</v>
       </c>
       <c r="B8" t="n">
-        <v>83371</v>
+        <v>83381</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>136702641</v>
       </c>
       <c r="B10" t="n">
-        <v>80619</v>
+        <v>80629</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>136702632</v>
       </c>
       <c r="B12" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3355,7 +3355,7 @@
         <v>136702660</v>
       </c>
       <c r="B28" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         <v>136702661</v>
       </c>
       <c r="B29" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         <v>136702630</v>
       </c>
       <c r="B30" t="n">
-        <v>83494</v>
+        <v>83504</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>136702644</v>
       </c>
       <c r="B31" t="n">
-        <v>80512</v>
+        <v>80522</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         <v>136702645</v>
       </c>
       <c r="B32" t="n">
-        <v>80512</v>
+        <v>80522</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>136702650</v>
       </c>
       <c r="B36" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         <v>136702636</v>
       </c>
       <c r="B40" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         <v>136702634</v>
       </c>
       <c r="B48" t="n">
-        <v>110141</v>
+        <v>110162</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
